--- a/artfynd/A 9885-2024 artfynd.xlsx
+++ b/artfynd/A 9885-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124482428</v>
+        <v>124482422</v>
       </c>
       <c r="B2" t="n">
-        <v>58191</v>
+        <v>58055</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103044</v>
+        <v>102990</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -715,7 +715,11 @@
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -795,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124482422</v>
+        <v>124482412</v>
       </c>
       <c r="B3" t="n">
-        <v>58055</v>
+        <v>57761</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,30 +811,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102990</v>
+        <v>103012</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -919,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124482412</v>
+        <v>124482428</v>
       </c>
       <c r="B4" t="n">
-        <v>57761</v>
+        <v>58191</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,39 +935,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103012</v>
+        <v>103044</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>

--- a/artfynd/A 9885-2024 artfynd.xlsx
+++ b/artfynd/A 9885-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124482422</v>
+        <v>124482428</v>
       </c>
       <c r="B2" t="n">
-        <v>58055</v>
+        <v>58191</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102990</v>
+        <v>103044</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -715,11 +715,7 @@
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -923,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124482428</v>
+        <v>124482422</v>
       </c>
       <c r="B4" t="n">
-        <v>58191</v>
+        <v>58055</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,16 +935,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103044</v>
+        <v>102990</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -963,7 +959,11 @@
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>

--- a/artfynd/A 9885-2024 artfynd.xlsx
+++ b/artfynd/A 9885-2024 artfynd.xlsx
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124482412</v>
+        <v>124482422</v>
       </c>
       <c r="B3" t="n">
-        <v>57761</v>
+        <v>58055</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,30 +807,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103012</v>
+        <v>102990</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124482422</v>
+        <v>124482412</v>
       </c>
       <c r="B4" t="n">
-        <v>58055</v>
+        <v>57761</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,30 +931,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102990</v>
+        <v>103012</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>

--- a/artfynd/A 9885-2024 artfynd.xlsx
+++ b/artfynd/A 9885-2024 artfynd.xlsx
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124482422</v>
+        <v>124482412</v>
       </c>
       <c r="B3" t="n">
-        <v>58055</v>
+        <v>57761</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,30 +807,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102990</v>
+        <v>103012</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124482412</v>
+        <v>124482422</v>
       </c>
       <c r="B4" t="n">
-        <v>57761</v>
+        <v>58055</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,30 +931,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103012</v>
+        <v>102990</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>

--- a/artfynd/A 9885-2024 artfynd.xlsx
+++ b/artfynd/A 9885-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124482428</v>
+        <v>124482422</v>
       </c>
       <c r="B2" t="n">
-        <v>58191</v>
+        <v>58055</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103044</v>
+        <v>102990</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -715,7 +715,11 @@
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -795,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124482412</v>
+        <v>124482428</v>
       </c>
       <c r="B3" t="n">
-        <v>57761</v>
+        <v>58191</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,39 +811,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103012</v>
+        <v>103044</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124482422</v>
+        <v>124482412</v>
       </c>
       <c r="B4" t="n">
-        <v>58055</v>
+        <v>57761</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,30 +931,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102990</v>
+        <v>103012</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>

--- a/artfynd/A 9885-2024 artfynd.xlsx
+++ b/artfynd/A 9885-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124482422</v>
+        <v>124482428</v>
       </c>
       <c r="B2" t="n">
-        <v>58055</v>
+        <v>58191</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102990</v>
+        <v>103044</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -715,11 +715,7 @@
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -799,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124482428</v>
+        <v>124482412</v>
       </c>
       <c r="B3" t="n">
-        <v>58191</v>
+        <v>57761</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,35 +807,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103044</v>
+        <v>103012</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124482412</v>
+        <v>124482422</v>
       </c>
       <c r="B4" t="n">
-        <v>57761</v>
+        <v>58055</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,30 +931,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103012</v>
+        <v>102990</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>

--- a/artfynd/A 9885-2024 artfynd.xlsx
+++ b/artfynd/A 9885-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124482428</v>
+        <v>124482412</v>
       </c>
       <c r="B2" t="n">
-        <v>58191</v>
+        <v>57761</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103044</v>
+        <v>103012</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -795,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124482412</v>
+        <v>124482422</v>
       </c>
       <c r="B3" t="n">
-        <v>57761</v>
+        <v>58055</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,30 +811,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103012</v>
+        <v>102990</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -919,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124482422</v>
+        <v>124482428</v>
       </c>
       <c r="B4" t="n">
-        <v>58055</v>
+        <v>58191</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,16 +939,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102990</v>
+        <v>103044</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -959,11 +963,7 @@
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>

--- a/artfynd/A 9885-2024 artfynd.xlsx
+++ b/artfynd/A 9885-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124482412</v>
+        <v>124482422</v>
       </c>
       <c r="B2" t="n">
-        <v>57761</v>
+        <v>58055</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103012</v>
+        <v>102990</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124482422</v>
+        <v>124482428</v>
       </c>
       <c r="B3" t="n">
-        <v>58055</v>
+        <v>58191</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,16 +815,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102990</v>
+        <v>103044</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -839,11 +839,7 @@
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -923,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124482428</v>
+        <v>124482412</v>
       </c>
       <c r="B4" t="n">
-        <v>58191</v>
+        <v>57761</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,35 +931,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103044</v>
+        <v>103012</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>

--- a/artfynd/A 9885-2024 artfynd.xlsx
+++ b/artfynd/A 9885-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124482422</v>
+        <v>124482412</v>
       </c>
       <c r="B2" t="n">
-        <v>58055</v>
+        <v>57761</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102990</v>
+        <v>103012</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124482428</v>
+        <v>124482422</v>
       </c>
       <c r="B3" t="n">
-        <v>58191</v>
+        <v>58055</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,16 +815,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103044</v>
+        <v>102990</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -839,7 +839,11 @@
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -919,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124482412</v>
+        <v>124482428</v>
       </c>
       <c r="B4" t="n">
-        <v>57761</v>
+        <v>58191</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,39 +935,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103012</v>
+        <v>103044</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>

--- a/artfynd/A 9885-2024 artfynd.xlsx
+++ b/artfynd/A 9885-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124482412</v>
+        <v>124482428</v>
       </c>
       <c r="B2" t="n">
-        <v>57761</v>
+        <v>58191</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103012</v>
+        <v>103044</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -799,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124482422</v>
+        <v>124482412</v>
       </c>
       <c r="B3" t="n">
-        <v>58055</v>
+        <v>57761</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,30 +807,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102990</v>
+        <v>103012</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -923,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124482428</v>
+        <v>124482422</v>
       </c>
       <c r="B4" t="n">
-        <v>58191</v>
+        <v>58055</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,16 +935,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103044</v>
+        <v>102990</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -963,7 +959,11 @@
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>

--- a/artfynd/A 9885-2024 artfynd.xlsx
+++ b/artfynd/A 9885-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124482428</v>
+        <v>124482422</v>
       </c>
       <c r="B2" t="n">
-        <v>58191</v>
+        <v>58055</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103044</v>
+        <v>102990</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -715,7 +715,11 @@
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -919,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124482422</v>
+        <v>124482428</v>
       </c>
       <c r="B4" t="n">
-        <v>58055</v>
+        <v>58191</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,16 +939,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102990</v>
+        <v>103044</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -959,11 +963,7 @@
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
